--- a/fusionEntreesCDA/ig/StructureDefinition-fr-cda-dicom-quantite.xlsx
+++ b/fusionEntreesCDA/ig/StructureDefinition-fr-cda-dicom-quantite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T09:38:40+00:00</t>
+    <t>2026-04-20T06:44:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionEntreesCDA/ig/StructureDefinition-fr-cda-dicom-quantite.xlsx
+++ b/fusionEntreesCDA/ig/StructureDefinition-fr-cda-dicom-quantite.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$89</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$100</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2819" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3168" uniqueCount="315">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T06:44:24+00:00</t>
+    <t>2026-04-20T07:29:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -523,6 +523,132 @@
     <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-quantite-exposition-rayonnements-cisis</t>
   </si>
   <si>
+    <t>Observation.code.nullFlavor</t>
+  </si>
+  <si>
+    <t>Observation.code.code</t>
+  </si>
+  <si>
+    <t>The plain code symbol defined by the code system. For example, "784.0" is the code symbol of the ICD-9 code "784.0" for headache.</t>
+  </si>
+  <si>
+    <t>CD.code</t>
+  </si>
+  <si>
+    <t>Observation.code.codeSystem</t>
+  </si>
+  <si>
+    <t>Code System</t>
+  </si>
+  <si>
+    <t>Specifies the code system that defines the code.</t>
+  </si>
+  <si>
+    <t>CD.codeSystem</t>
+  </si>
+  <si>
+    <t>Observation.code.codeSystemName</t>
+  </si>
+  <si>
+    <t>Code System Name</t>
+  </si>
+  <si>
+    <t>The common name of the coding system.</t>
+  </si>
+  <si>
+    <t>CD.codeSystemName</t>
+  </si>
+  <si>
+    <t>Observation.code.codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Code System Version</t>
+  </si>
+  <si>
+    <t>If applicable, a version descriptor defined specifically for the given code system.</t>
+  </si>
+  <si>
+    <t>CD.codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Observation.code.displayName</t>
+  </si>
+  <si>
+    <t>Display Name</t>
+  </si>
+  <si>
+    <t>A name or title for the code, under which the sending system shows the code value to its users.</t>
+  </si>
+  <si>
+    <t>CD.displayName</t>
+  </si>
+  <si>
+    <t>Observation.code.sdtcValueSet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string {http://hl7.org/cda/stds/core/StructureDefinition/oid}
+</t>
+  </si>
+  <si>
+    <t>The valueSet extension adds an attribute for elements with a CD dataType which indicates the particular value set constraining the coded concept.</t>
+  </si>
+  <si>
+    <t>CD.valueSet</t>
+  </si>
+  <si>
+    <t>Observation.code.sdtcValueSetVersion</t>
+  </si>
+  <si>
+    <t>The valueSetVersion extension adds an attribute for elements with a CD dataType which indicates the version of the particular value set constraining the coded concept.</t>
+  </si>
+  <si>
+    <t>CD.sdtcValueSetVersion</t>
+  </si>
+  <si>
+    <t>Observation.code.originalText</t>
+  </si>
+  <si>
+    <t>Original Text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/ED
+</t>
+  </si>
+  <si>
+    <t>The text or phrase used as the basis for the coding.</t>
+  </si>
+  <si>
+    <t>CD.originalText</t>
+  </si>
+  <si>
+    <t>Observation.code.qualifier</t>
+  </si>
+  <si>
+    <t>Qualifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/CR
+</t>
+  </si>
+  <si>
+    <t>Specifies additional codes that increase the specificity of the the primary code.</t>
+  </si>
+  <si>
+    <t>CD.qualifier</t>
+  </si>
+  <si>
+    <t>Observation.code.translation</t>
+  </si>
+  <si>
+    <t>Translation</t>
+  </si>
+  <si>
+    <t>A set of other concept descriptors that translate this concept descriptor into other code systems.</t>
+  </si>
+  <si>
+    <t>CD.translation</t>
+  </si>
+  <si>
     <t>Observation.derivationExpr</t>
   </si>
   <si>
@@ -533,10 +659,6 @@
     <t>Observation.text</t>
   </si>
   <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/ED
-</t>
-  </si>
-  <si>
     <t>Partie narrative de l'entrée</t>
   </si>
   <si>
@@ -625,108 +747,31 @@
     <t>Observation.targetSiteCode.code</t>
   </si>
   <si>
-    <t>The plain code symbol defined by the code system. For example, "784.0" is the code symbol of the ICD-9 code "784.0" for headache.</t>
-  </si>
-  <si>
-    <t>CD.code</t>
-  </si>
-  <si>
     <t>Observation.targetSiteCode.codeSystem</t>
   </si>
   <si>
-    <t>Code System</t>
-  </si>
-  <si>
-    <t>Specifies the code system that defines the code.</t>
-  </si>
-  <si>
-    <t>CD.codeSystem</t>
-  </si>
-  <si>
     <t>Observation.targetSiteCode.codeSystemName</t>
   </si>
   <si>
-    <t>Code System Name</t>
-  </si>
-  <si>
-    <t>The common name of the coding system.</t>
-  </si>
-  <si>
-    <t>CD.codeSystemName</t>
-  </si>
-  <si>
     <t>Observation.targetSiteCode.codeSystemVersion</t>
   </si>
   <si>
-    <t>Code System Version</t>
-  </si>
-  <si>
-    <t>If applicable, a version descriptor defined specifically for the given code system.</t>
-  </si>
-  <si>
-    <t>CD.codeSystemVersion</t>
-  </si>
-  <si>
     <t>Observation.targetSiteCode.displayName</t>
   </si>
   <si>
-    <t>Display Name</t>
-  </si>
-  <si>
-    <t>A name or title for the code, under which the sending system shows the code value to its users.</t>
-  </si>
-  <si>
-    <t>CD.displayName</t>
-  </si>
-  <si>
     <t>Observation.targetSiteCode.sdtcValueSet</t>
   </si>
   <si>
-    <t xml:space="preserve">string {http://hl7.org/cda/stds/core/StructureDefinition/oid}
-</t>
-  </si>
-  <si>
-    <t>The valueSet extension adds an attribute for elements with a CD dataType which indicates the particular value set constraining the coded concept.</t>
-  </si>
-  <si>
-    <t>CD.valueSet</t>
-  </si>
-  <si>
     <t>Observation.targetSiteCode.sdtcValueSetVersion</t>
   </si>
   <si>
-    <t>The valueSetVersion extension adds an attribute for elements with a CD dataType which indicates the version of the particular value set constraining the coded concept.</t>
-  </si>
-  <si>
-    <t>CD.sdtcValueSetVersion</t>
-  </si>
-  <si>
     <t>Observation.targetSiteCode.originalText</t>
   </si>
   <si>
-    <t>Original Text</t>
-  </si>
-  <si>
-    <t>The text or phrase used as the basis for the coding.</t>
-  </si>
-  <si>
-    <t>CD.originalText</t>
-  </si>
-  <si>
     <t>Observation.targetSiteCode.qualifier</t>
   </si>
   <si>
-    <t>Qualifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/CR
-</t>
-  </si>
-  <si>
     <t>Précision topographique</t>
-  </si>
-  <si>
-    <t>CD.qualifier</t>
   </si>
   <si>
     <t>Observation.targetSiteCode.qualifier.nullFlavor</t>
@@ -803,19 +848,7 @@
     <t>Observation.targetSiteCode.qualifier.name.qualifier</t>
   </si>
   <si>
-    <t>Specifies additional codes that increase the specificity of the the primary code.</t>
-  </si>
-  <si>
     <t>Observation.targetSiteCode.qualifier.name.translation</t>
-  </si>
-  <si>
-    <t>Translation</t>
-  </si>
-  <si>
-    <t>A set of other concept descriptors that translate this concept descriptor into other code systems.</t>
-  </si>
-  <si>
-    <t>CD.translation</t>
   </si>
   <si>
     <t>Observation.targetSiteCode.qualifier.value</t>
@@ -1277,7 +1310,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK89"/>
+  <dimension ref="A1:AK100"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="62.33203125" customWidth="true" bestFit="true"/>
@@ -3978,7 +4011,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
         <v>158</v>
       </c>
@@ -3997,7 +4030,7 @@
         <v>75</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>74</v>
@@ -4292,7 +4325,9 @@
       <c r="D30" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E30" s="2"/>
+      <c r="E30" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F30" t="s" s="2">
         <v>80</v>
       </c>
@@ -4309,10 +4344,12 @@
         <v>74</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>166</v>
+        <v>85</v>
       </c>
       <c r="L30" s="2"/>
-      <c r="M30" s="2"/>
+      <c r="M30" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4338,13 +4375,11 @@
         <v>74</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y30" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y30" s="2"/>
       <c r="Z30" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>74</v>
@@ -4362,7 +4397,7 @@
         <v>74</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>165</v>
+        <v>89</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -4382,18 +4417,20 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E31" s="2"/>
+      <c r="E31" t="s" s="2">
+        <v>62</v>
+      </c>
       <c r="F31" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>75</v>
@@ -4408,13 +4445,11 @@
         <v>74</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="L31" t="s" s="2">
-        <v>169</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="L31" s="2"/>
       <c r="M31" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4465,7 +4500,7 @@
         <v>74</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -4485,16 +4520,18 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E32" s="2"/>
+      <c r="E32" t="s" s="2">
+        <v>170</v>
+      </c>
       <c r="F32" t="s" s="2">
         <v>75</v>
       </c>
@@ -4511,11 +4548,9 @@
         <v>74</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="L32" t="s" s="2">
-        <v>171</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="L32" s="2"/>
       <c r="M32" t="s" s="2">
         <v>171</v>
       </c>
@@ -4544,30 +4579,32 @@
         <v>74</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y32" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF32" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="AA32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE32" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF32" t="s" s="2">
-        <v>170</v>
-      </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
@@ -4584,7 +4621,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
         <v>173</v>
       </c>
@@ -4595,7 +4632,9 @@
       <c r="D33" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E33" s="2"/>
+      <c r="E33" t="s" s="2">
+        <v>174</v>
+      </c>
       <c r="F33" t="s" s="2">
         <v>80</v>
       </c>
@@ -4603,7 +4642,7 @@
         <v>75</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>74</v>
@@ -4612,11 +4651,9 @@
         <v>74</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="L33" t="s" s="2">
-        <v>175</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="L33" s="2"/>
       <c r="M33" t="s" s="2">
         <v>175</v>
       </c>
@@ -4669,7 +4706,7 @@
         <v>74</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -4689,16 +4726,18 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E34" s="2"/>
+      <c r="E34" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="F34" t="s" s="2">
         <v>80</v>
       </c>
@@ -4715,10 +4754,12 @@
         <v>74</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>177</v>
+        <v>102</v>
       </c>
       <c r="L34" s="2"/>
-      <c r="M34" s="2"/>
+      <c r="M34" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -4744,11 +4785,13 @@
         <v>74</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="Y34" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z34" t="s" s="2">
-        <v>179</v>
+        <v>74</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>74</v>
@@ -4766,7 +4809,7 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -4784,26 +4827,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E35" s="2"/>
+      <c r="E35" t="s" s="2">
+        <v>182</v>
+      </c>
       <c r="F35" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>74</v>
@@ -4812,10 +4857,12 @@
         <v>74</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>181</v>
+        <v>102</v>
       </c>
       <c r="L35" s="2"/>
-      <c r="M35" s="2"/>
+      <c r="M35" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -4865,7 +4912,7 @@
         <v>74</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -4885,10 +4932,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4911,10 +4958,12 @@
         <v>74</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>91</v>
+        <v>186</v>
       </c>
       <c r="L36" s="2"/>
-      <c r="M36" s="2"/>
+      <c r="M36" t="s" s="2">
+        <v>187</v>
+      </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -4940,11 +4989,13 @@
         <v>74</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y36" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z36" t="s" s="2">
-        <v>183</v>
+        <v>74</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>74</v>
@@ -4962,7 +5013,7 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -4980,12 +5031,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4993,13 +5044,13 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>74</v>
@@ -5008,10 +5059,12 @@
         <v>74</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>185</v>
+        <v>102</v>
       </c>
       <c r="L37" s="2"/>
-      <c r="M37" s="2"/>
+      <c r="M37" t="s" s="2">
+        <v>190</v>
+      </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5061,13 +5114,13 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>74</v>
@@ -5079,18 +5132,20 @@
         <v>74</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E38" s="2"/>
+      <c r="E38" t="s" s="2">
+        <v>193</v>
+      </c>
       <c r="F38" t="s" s="2">
         <v>80</v>
       </c>
@@ -5098,7 +5153,7 @@
         <v>75</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>74</v>
@@ -5107,13 +5162,11 @@
         <v>74</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="L38" t="s" s="2">
-        <v>187</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="L38" s="2"/>
       <c r="M38" t="s" s="2">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5140,11 +5193,13 @@
         <v>74</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y38" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z38" t="s" s="2">
-        <v>188</v>
+        <v>74</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>74</v>
@@ -5162,13 +5217,13 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>74</v>
@@ -5180,26 +5235,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E39" s="2"/>
+      <c r="E39" t="s" s="2">
+        <v>198</v>
+      </c>
       <c r="F39" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>74</v>
@@ -5208,13 +5265,11 @@
         <v>74</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="L39" t="s" s="2">
-        <v>190</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="L39" s="2"/>
       <c r="M39" t="s" s="2">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5241,11 +5296,13 @@
         <v>74</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="Y39" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z39" t="s" s="2">
-        <v>191</v>
+        <v>74</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>74</v>
@@ -5263,7 +5320,7 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -5283,21 +5340,23 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E40" s="2"/>
+      <c r="E40" t="s" s="2">
+        <v>203</v>
+      </c>
       <c r="F40" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>74</v>
@@ -5311,11 +5370,9 @@
       <c r="K40" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="L40" t="s" s="2">
-        <v>193</v>
-      </c>
+      <c r="L40" s="2"/>
       <c r="M40" t="s" s="2">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5366,7 +5423,7 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -5386,18 +5443,16 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E41" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>80</v>
       </c>
@@ -5414,12 +5469,10 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>85</v>
+        <v>207</v>
       </c>
       <c r="L41" s="2"/>
-      <c r="M41" t="s" s="2">
-        <v>86</v>
-      </c>
+      <c r="M41" s="2"/>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -5445,11 +5498,13 @@
         <v>74</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y41" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z41" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>74</v>
@@ -5467,7 +5522,7 @@
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>89</v>
+        <v>206</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -5485,20 +5540,18 @@
         <v>74</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E42" t="s" s="2">
-        <v>62</v>
-      </c>
+      <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>80</v>
       </c>
@@ -5506,7 +5559,7 @@
         <v>75</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>74</v>
@@ -5515,11 +5568,13 @@
         <v>74</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L42" s="2"/>
+        <v>194</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>209</v>
+      </c>
       <c r="M42" t="s" s="2">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5570,7 +5625,7 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -5588,28 +5643,26 @@
         <v>74</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E43" t="s" s="2">
-        <v>200</v>
-      </c>
+      <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>74</v>
@@ -5618,11 +5671,13 @@
         <v>74</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="L43" s="2"/>
+        <v>91</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>211</v>
+      </c>
       <c r="M43" t="s" s="2">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5649,13 +5704,11 @@
         <v>74</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y43" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y43" s="2"/>
       <c r="Z43" t="s" s="2">
-        <v>74</v>
+        <v>212</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>74</v>
@@ -5673,7 +5726,7 @@
         <v>74</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -5691,20 +5744,18 @@
         <v>74</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E44" t="s" s="2">
-        <v>204</v>
-      </c>
+      <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>80</v>
       </c>
@@ -5712,7 +5763,7 @@
         <v>75</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>74</v>
@@ -5721,11 +5772,13 @@
         <v>74</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="L44" s="2"/>
+        <v>214</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>215</v>
+      </c>
       <c r="M44" t="s" s="2">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -5776,7 +5829,7 @@
         <v>74</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -5796,18 +5849,16 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E45" t="s" s="2">
-        <v>208</v>
-      </c>
+      <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>80</v>
       </c>
@@ -5824,12 +5875,10 @@
         <v>74</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>102</v>
+        <v>217</v>
       </c>
       <c r="L45" s="2"/>
-      <c r="M45" t="s" s="2">
-        <v>209</v>
-      </c>
+      <c r="M45" s="2"/>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -5855,13 +5904,11 @@
         <v>74</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y45" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="Y45" s="2"/>
       <c r="Z45" t="s" s="2">
-        <v>74</v>
+        <v>219</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>74</v>
@@ -5879,7 +5926,7 @@
         <v>74</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -5899,18 +5946,16 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E46" t="s" s="2">
-        <v>212</v>
-      </c>
+      <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>80</v>
       </c>
@@ -5927,12 +5972,10 @@
         <v>74</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>102</v>
+        <v>221</v>
       </c>
       <c r="L46" s="2"/>
-      <c r="M46" t="s" s="2">
-        <v>213</v>
-      </c>
+      <c r="M46" s="2"/>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -5982,7 +6025,7 @@
         <v>74</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -6002,10 +6045,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6028,12 +6071,10 @@
         <v>74</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>216</v>
+        <v>91</v>
       </c>
       <c r="L47" s="2"/>
-      <c r="M47" t="s" s="2">
-        <v>217</v>
-      </c>
+      <c r="M47" s="2"/>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6059,13 +6100,11 @@
         <v>74</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y47" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y47" s="2"/>
       <c r="Z47" t="s" s="2">
-        <v>74</v>
+        <v>223</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>74</v>
@@ -6083,7 +6122,7 @@
         <v>74</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -6101,12 +6140,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6114,13 +6153,13 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>74</v>
@@ -6129,12 +6168,10 @@
         <v>74</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>102</v>
+        <v>225</v>
       </c>
       <c r="L48" s="2"/>
-      <c r="M48" t="s" s="2">
-        <v>220</v>
-      </c>
+      <c r="M48" s="2"/>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6184,13 +6221,13 @@
         <v>74</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>74</v>
@@ -6202,20 +6239,18 @@
         <v>74</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E49" t="s" s="2">
-        <v>223</v>
-      </c>
+      <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>80</v>
       </c>
@@ -6223,7 +6258,7 @@
         <v>75</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>74</v>
@@ -6232,11 +6267,13 @@
         <v>74</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="L49" s="2"/>
+        <v>217</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="M49" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -6263,13 +6300,11 @@
         <v>74</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y49" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y49" s="2"/>
       <c r="Z49" t="s" s="2">
-        <v>74</v>
+        <v>228</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>74</v>
@@ -6287,13 +6322,13 @@
         <v>74</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>74</v>
@@ -6307,18 +6342,16 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E50" t="s" s="2">
-        <v>227</v>
-      </c>
+      <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>80</v>
       </c>
@@ -6335,13 +6368,13 @@
         <v>74</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -6368,13 +6401,11 @@
         <v>74</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y50" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="Y50" s="2"/>
       <c r="Z50" t="s" s="2">
-        <v>74</v>
+        <v>231</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>74</v>
@@ -6392,7 +6423,7 @@
         <v>74</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -6412,20 +6443,18 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E51" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>75</v>
@@ -6440,11 +6469,13 @@
         <v>74</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L51" s="2"/>
+        <v>161</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>233</v>
+      </c>
       <c r="M51" t="s" s="2">
-        <v>86</v>
+        <v>234</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -6471,11 +6502,13 @@
         <v>74</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y51" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z51" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>74</v>
@@ -6493,13 +6526,13 @@
         <v>74</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>89</v>
+        <v>232</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>74</v>
@@ -6513,17 +6546,17 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E52" t="s" s="2">
-        <v>233</v>
+        <v>84</v>
       </c>
       <c r="F52" t="s" s="2">
         <v>80</v>
@@ -6541,11 +6574,11 @@
         <v>74</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>234</v>
+        <v>85</v>
       </c>
       <c r="L52" s="2"/>
       <c r="M52" t="s" s="2">
-        <v>235</v>
+        <v>86</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -6572,13 +6605,11 @@
         <v>74</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y52" s="2"/>
       <c r="Z52" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>74</v>
@@ -6596,46 +6627,46 @@
         <v>74</v>
       </c>
       <c r="AF52" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK52" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="53" hidden="true">
+      <c r="A53" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="AG52" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH52" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI52" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ52" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK52" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="s" s="2">
-        <v>237</v>
-      </c>
       <c r="B53" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E53" t="s" s="2">
-        <v>6</v>
+        <v>62</v>
       </c>
       <c r="F53" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>74</v>
@@ -6644,11 +6675,11 @@
         <v>74</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>238</v>
+        <v>85</v>
       </c>
       <c r="L53" s="2"/>
       <c r="M53" t="s" s="2">
-        <v>239</v>
+        <v>167</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -6699,7 +6730,7 @@
         <v>74</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>240</v>
+        <v>168</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -6719,17 +6750,17 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E54" t="s" s="2">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c r="F54" t="s" s="2">
         <v>80</v>
@@ -6747,11 +6778,11 @@
         <v>74</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>85</v>
+        <v>112</v>
       </c>
       <c r="L54" s="2"/>
       <c r="M54" t="s" s="2">
-        <v>86</v>
+        <v>171</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -6778,11 +6809,13 @@
         <v>74</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y54" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z54" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>74</v>
@@ -6800,7 +6833,7 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>89</v>
+        <v>172</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -6820,17 +6853,17 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E55" t="s" s="2">
-        <v>62</v>
+        <v>174</v>
       </c>
       <c r="F55" t="s" s="2">
         <v>80</v>
@@ -6848,11 +6881,11 @@
         <v>74</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="L55" s="2"/>
       <c r="M55" t="s" s="2">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -6864,7 +6897,7 @@
         <v>74</v>
       </c>
       <c r="S55" t="s" s="2">
-        <v>243</v>
+        <v>74</v>
       </c>
       <c r="T55" t="s" s="2">
         <v>74</v>
@@ -6903,7 +6936,7 @@
         <v>74</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -6923,17 +6956,17 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E56" t="s" s="2">
-        <v>200</v>
+        <v>178</v>
       </c>
       <c r="F56" t="s" s="2">
         <v>80</v>
@@ -6951,11 +6984,11 @@
         <v>74</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="L56" s="2"/>
       <c r="M56" t="s" s="2">
-        <v>201</v>
+        <v>179</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -6967,7 +7000,7 @@
         <v>74</v>
       </c>
       <c r="S56" t="s" s="2">
-        <v>245</v>
+        <v>74</v>
       </c>
       <c r="T56" t="s" s="2">
         <v>74</v>
@@ -7006,7 +7039,7 @@
         <v>74</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>202</v>
+        <v>180</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -7026,17 +7059,17 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E57" t="s" s="2">
-        <v>204</v>
+        <v>182</v>
       </c>
       <c r="F57" t="s" s="2">
         <v>80</v>
@@ -7058,7 +7091,7 @@
       </c>
       <c r="L57" s="2"/>
       <c r="M57" t="s" s="2">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7070,7 +7103,7 @@
         <v>74</v>
       </c>
       <c r="S57" t="s" s="2">
-        <v>247</v>
+        <v>74</v>
       </c>
       <c r="T57" t="s" s="2">
         <v>74</v>
@@ -7109,7 +7142,7 @@
         <v>74</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>206</v>
+        <v>184</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -7129,18 +7162,16 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E58" t="s" s="2">
-        <v>208</v>
-      </c>
+      <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
         <v>80</v>
       </c>
@@ -7157,11 +7188,11 @@
         <v>74</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>102</v>
+        <v>186</v>
       </c>
       <c r="L58" s="2"/>
       <c r="M58" t="s" s="2">
-        <v>209</v>
+        <v>187</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -7212,7 +7243,7 @@
         <v>74</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>210</v>
+        <v>188</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -7232,18 +7263,16 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E59" t="s" s="2">
-        <v>212</v>
-      </c>
+      <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>80</v>
       </c>
@@ -7264,7 +7293,7 @@
       </c>
       <c r="L59" s="2"/>
       <c r="M59" t="s" s="2">
-        <v>213</v>
+        <v>190</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -7276,7 +7305,7 @@
         <v>74</v>
       </c>
       <c r="S59" t="s" s="2">
-        <v>250</v>
+        <v>74</v>
       </c>
       <c r="T59" t="s" s="2">
         <v>74</v>
@@ -7315,7 +7344,7 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>214</v>
+        <v>191</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -7335,16 +7364,18 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E60" s="2"/>
+      <c r="E60" t="s" s="2">
+        <v>193</v>
+      </c>
       <c r="F60" t="s" s="2">
         <v>80</v>
       </c>
@@ -7361,11 +7392,11 @@
         <v>74</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>216</v>
+        <v>194</v>
       </c>
       <c r="L60" s="2"/>
       <c r="M60" t="s" s="2">
-        <v>217</v>
+        <v>195</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -7416,7 +7447,7 @@
         <v>74</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -7434,18 +7465,20 @@
         <v>74</v>
       </c>
     </row>
-    <row r="61" hidden="true">
+    <row r="61">
       <c r="A61" t="s" s="2">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E61" s="2"/>
+      <c r="E61" t="s" s="2">
+        <v>198</v>
+      </c>
       <c r="F61" t="s" s="2">
         <v>80</v>
       </c>
@@ -7453,7 +7486,7 @@
         <v>75</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>74</v>
@@ -7462,11 +7495,13 @@
         <v>74</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="L61" s="2"/>
+        <v>199</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>245</v>
+      </c>
       <c r="M61" t="s" s="2">
-        <v>220</v>
+        <v>245</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -7517,13 +7552,13 @@
         <v>74</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>221</v>
+        <v>201</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>74</v>
@@ -7537,17 +7572,17 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E62" t="s" s="2">
-        <v>223</v>
+        <v>84</v>
       </c>
       <c r="F62" t="s" s="2">
         <v>80</v>
@@ -7565,11 +7600,11 @@
         <v>74</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>168</v>
+        <v>85</v>
       </c>
       <c r="L62" s="2"/>
       <c r="M62" t="s" s="2">
-        <v>224</v>
+        <v>86</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -7596,13 +7631,11 @@
         <v>74</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y62" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y62" s="2"/>
       <c r="Z62" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>74</v>
@@ -7620,7 +7653,7 @@
         <v>74</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>225</v>
+        <v>89</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -7640,23 +7673,23 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E63" t="s" s="2">
-        <v>227</v>
+        <v>248</v>
       </c>
       <c r="F63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>74</v>
@@ -7668,11 +7701,11 @@
         <v>74</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="L63" s="2"/>
       <c r="M63" t="s" s="2">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -7723,13 +7756,13 @@
         <v>74</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>230</v>
+        <v>251</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>74</v>
@@ -7741,28 +7774,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E64" t="s" s="2">
-        <v>257</v>
+        <v>6</v>
       </c>
       <c r="F64" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>74</v>
@@ -7771,11 +7804,11 @@
         <v>74</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>161</v>
+        <v>253</v>
       </c>
       <c r="L64" s="2"/>
       <c r="M64" t="s" s="2">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -7826,13 +7859,13 @@
         <v>74</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>74</v>
@@ -7844,28 +7877,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E65" t="s" s="2">
-        <v>1</v>
+        <v>84</v>
       </c>
       <c r="F65" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>74</v>
@@ -7874,13 +7907,11 @@
         <v>74</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="L65" t="s" s="2">
-        <v>261</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="L65" s="2"/>
       <c r="M65" t="s" s="2">
-        <v>261</v>
+        <v>86</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -7911,7 +7942,7 @@
       </c>
       <c r="Y65" s="2"/>
       <c r="Z65" t="s" s="2">
-        <v>262</v>
+        <v>88</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>74</v>
@@ -7929,7 +7960,7 @@
         <v>74</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>263</v>
+        <v>89</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -7949,23 +7980,23 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E66" t="s" s="2">
-        <v>257</v>
+        <v>62</v>
       </c>
       <c r="F66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>74</v>
@@ -7977,11 +8008,11 @@
         <v>74</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>161</v>
+        <v>85</v>
       </c>
       <c r="L66" s="2"/>
       <c r="M66" t="s" s="2">
-        <v>258</v>
+        <v>167</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -7993,7 +8024,7 @@
         <v>74</v>
       </c>
       <c r="S66" t="s" s="2">
-        <v>74</v>
+        <v>258</v>
       </c>
       <c r="T66" t="s" s="2">
         <v>74</v>
@@ -8032,13 +8063,13 @@
         <v>74</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>259</v>
+        <v>168</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>74</v>
@@ -8052,16 +8083,18 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E67" s="2"/>
+      <c r="E67" t="s" s="2">
+        <v>170</v>
+      </c>
       <c r="F67" t="s" s="2">
         <v>80</v>
       </c>
@@ -8078,10 +8111,12 @@
         <v>74</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>266</v>
+        <v>112</v>
       </c>
       <c r="L67" s="2"/>
-      <c r="M67" s="2"/>
+      <c r="M67" t="s" s="2">
+        <v>171</v>
+      </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -8092,7 +8127,7 @@
         <v>74</v>
       </c>
       <c r="S67" t="s" s="2">
-        <v>74</v>
+        <v>260</v>
       </c>
       <c r="T67" t="s" s="2">
         <v>74</v>
@@ -8131,7 +8166,7 @@
         <v>74</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>265</v>
+        <v>172</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -8151,21 +8186,23 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E68" s="2"/>
+      <c r="E68" t="s" s="2">
+        <v>174</v>
+      </c>
       <c r="F68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>74</v>
@@ -8177,10 +8214,12 @@
         <v>74</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>268</v>
+        <v>102</v>
       </c>
       <c r="L68" s="2"/>
-      <c r="M68" s="2"/>
+      <c r="M68" t="s" s="2">
+        <v>175</v>
+      </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -8191,7 +8230,7 @@
         <v>74</v>
       </c>
       <c r="S68" t="s" s="2">
-        <v>74</v>
+        <v>262</v>
       </c>
       <c r="T68" t="s" s="2">
         <v>74</v>
@@ -8230,13 +8269,13 @@
         <v>74</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>267</v>
+        <v>176</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>74</v>
@@ -8250,21 +8289,23 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E69" s="2"/>
+      <c r="E69" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="F69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>74</v>
@@ -8276,10 +8317,12 @@
         <v>74</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>270</v>
+        <v>102</v>
       </c>
       <c r="L69" s="2"/>
-      <c r="M69" s="2"/>
+      <c r="M69" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -8329,13 +8372,13 @@
         <v>74</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>269</v>
+        <v>180</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>74</v>
@@ -8349,21 +8392,23 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E70" s="2"/>
+      <c r="E70" t="s" s="2">
+        <v>182</v>
+      </c>
       <c r="F70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>74</v>
@@ -8375,10 +8420,12 @@
         <v>74</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>272</v>
+        <v>102</v>
       </c>
       <c r="L70" s="2"/>
-      <c r="M70" s="2"/>
+      <c r="M70" t="s" s="2">
+        <v>183</v>
+      </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -8389,7 +8436,7 @@
         <v>74</v>
       </c>
       <c r="S70" t="s" s="2">
-        <v>74</v>
+        <v>265</v>
       </c>
       <c r="T70" t="s" s="2">
         <v>74</v>
@@ -8428,13 +8475,13 @@
         <v>74</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>271</v>
+        <v>184</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>74</v>
@@ -8448,10 +8495,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8462,7 +8509,7 @@
         <v>80</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>74</v>
@@ -8474,10 +8521,12 @@
         <v>74</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>274</v>
+        <v>186</v>
       </c>
       <c r="L71" s="2"/>
-      <c r="M71" s="2"/>
+      <c r="M71" t="s" s="2">
+        <v>187</v>
+      </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -8527,13 +8576,13 @@
         <v>74</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>273</v>
+        <v>188</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>74</v>
@@ -8547,10 +8596,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8561,7 +8610,7 @@
         <v>80</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>74</v>
@@ -8573,10 +8622,12 @@
         <v>74</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>276</v>
+        <v>102</v>
       </c>
       <c r="L72" s="2"/>
-      <c r="M72" s="2"/>
+      <c r="M72" t="s" s="2">
+        <v>190</v>
+      </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -8626,13 +8677,13 @@
         <v>74</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>275</v>
+        <v>191</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>74</v>
@@ -8646,21 +8697,23 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E73" s="2"/>
+      <c r="E73" t="s" s="2">
+        <v>193</v>
+      </c>
       <c r="F73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>74</v>
@@ -8672,10 +8725,12 @@
         <v>74</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>278</v>
+        <v>194</v>
       </c>
       <c r="L73" s="2"/>
-      <c r="M73" s="2"/>
+      <c r="M73" t="s" s="2">
+        <v>195</v>
+      </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -8725,13 +8780,13 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>277</v>
+        <v>196</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>74</v>
@@ -8745,21 +8800,23 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E74" s="2"/>
+      <c r="E74" t="s" s="2">
+        <v>198</v>
+      </c>
       <c r="F74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>74</v>
@@ -8771,10 +8828,12 @@
         <v>74</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>280</v>
+        <v>199</v>
       </c>
       <c r="L74" s="2"/>
-      <c r="M74" s="2"/>
+      <c r="M74" t="s" s="2">
+        <v>200</v>
+      </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -8824,7 +8883,7 @@
         <v>74</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>279</v>
+        <v>201</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -8844,21 +8903,23 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E75" s="2"/>
+      <c r="E75" t="s" s="2">
+        <v>203</v>
+      </c>
       <c r="F75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>74</v>
@@ -8870,10 +8931,12 @@
         <v>74</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>282</v>
+        <v>161</v>
       </c>
       <c r="L75" s="2"/>
-      <c r="M75" s="2"/>
+      <c r="M75" t="s" s="2">
+        <v>204</v>
+      </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -8923,7 +8986,7 @@
         <v>74</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>281</v>
+        <v>205</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -8941,26 +9004,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="76" hidden="true">
+    <row r="76">
       <c r="A76" t="s" s="2">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>283</v>
+        <v>271</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E76" s="2"/>
+      <c r="E76" t="s" s="2">
+        <v>1</v>
+      </c>
       <c r="F76" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>74</v>
@@ -8969,10 +9034,14 @@
         <v>74</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="L76" s="2"/>
-      <c r="M76" s="2"/>
+        <v>161</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>272</v>
+      </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -8998,13 +9067,11 @@
         <v>74</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y76" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y76" s="2"/>
       <c r="Z76" t="s" s="2">
-        <v>74</v>
+        <v>273</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>74</v>
@@ -9022,13 +9089,13 @@
         <v>74</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>74</v>
@@ -9042,16 +9109,18 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E77" s="2"/>
+      <c r="E77" t="s" s="2">
+        <v>203</v>
+      </c>
       <c r="F77" t="s" s="2">
         <v>80</v>
       </c>
@@ -9068,11 +9137,11 @@
         <v>74</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>286</v>
+        <v>161</v>
       </c>
       <c r="L77" s="2"/>
       <c r="M77" t="s" s="2">
-        <v>287</v>
+        <v>204</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -9123,7 +9192,7 @@
         <v>74</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>285</v>
+        <v>205</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -9143,18 +9212,16 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>288</v>
+        <v>276</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E78" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
         <v>80</v>
       </c>
@@ -9171,12 +9238,10 @@
         <v>74</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>85</v>
+        <v>277</v>
       </c>
       <c r="L78" s="2"/>
-      <c r="M78" t="s" s="2">
-        <v>86</v>
-      </c>
+      <c r="M78" s="2"/>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -9202,11 +9267,13 @@
         <v>74</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y78" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z78" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>74</v>
@@ -9224,7 +9291,7 @@
         <v>74</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>89</v>
+        <v>276</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -9244,10 +9311,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9270,12 +9337,10 @@
         <v>74</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>91</v>
+        <v>279</v>
       </c>
       <c r="L79" s="2"/>
-      <c r="M79" t="s" s="2">
-        <v>92</v>
-      </c>
+      <c r="M79" s="2"/>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -9325,7 +9390,7 @@
         <v>74</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>93</v>
+        <v>278</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -9345,10 +9410,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9359,7 +9424,7 @@
         <v>80</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>74</v>
@@ -9371,12 +9436,10 @@
         <v>74</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>95</v>
+        <v>281</v>
       </c>
       <c r="L80" s="2"/>
-      <c r="M80" t="s" s="2">
-        <v>96</v>
-      </c>
+      <c r="M80" s="2"/>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -9426,19 +9489,19 @@
         <v>74</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>97</v>
+        <v>280</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>74</v>
@@ -9446,23 +9509,21 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E81" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>74</v>
@@ -9474,12 +9535,10 @@
         <v>74</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>85</v>
+        <v>283</v>
       </c>
       <c r="L81" s="2"/>
-      <c r="M81" t="s" s="2">
-        <v>86</v>
-      </c>
+      <c r="M81" s="2"/>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -9505,11 +9564,13 @@
         <v>74</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y81" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z81" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>74</v>
@@ -9527,13 +9588,13 @@
         <v>74</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>89</v>
+        <v>282</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>74</v>
@@ -9547,23 +9608,21 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E82" t="s" s="2">
-        <v>101</v>
-      </c>
+      <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>74</v>
@@ -9575,12 +9634,10 @@
         <v>74</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>102</v>
+        <v>285</v>
       </c>
       <c r="L82" s="2"/>
-      <c r="M82" t="s" s="2">
-        <v>103</v>
-      </c>
+      <c r="M82" s="2"/>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -9630,13 +9687,13 @@
         <v>74</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>104</v>
+        <v>284</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>74</v>
@@ -9650,23 +9707,21 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E83" t="s" s="2">
-        <v>106</v>
-      </c>
+      <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>74</v>
@@ -9678,12 +9733,10 @@
         <v>74</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>107</v>
+        <v>287</v>
       </c>
       <c r="L83" s="2"/>
-      <c r="M83" t="s" s="2">
-        <v>108</v>
-      </c>
+      <c r="M83" s="2"/>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -9733,13 +9786,13 @@
         <v>74</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>109</v>
+        <v>286</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>74</v>
@@ -9753,23 +9806,21 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E84" t="s" s="2">
-        <v>111</v>
-      </c>
+      <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>74</v>
@@ -9781,12 +9832,10 @@
         <v>74</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>112</v>
+        <v>289</v>
       </c>
       <c r="L84" s="2"/>
-      <c r="M84" t="s" s="2">
-        <v>113</v>
-      </c>
+      <c r="M84" s="2"/>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -9794,7 +9843,7 @@
       </c>
       <c r="Q84" s="2"/>
       <c r="R84" t="s" s="2">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="S84" t="s" s="2">
         <v>74</v>
@@ -9836,13 +9885,13 @@
         <v>74</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>115</v>
+        <v>288</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>74</v>
@@ -9856,23 +9905,21 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E85" t="s" s="2">
-        <v>117</v>
-      </c>
+      <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>74</v>
@@ -9884,12 +9931,10 @@
         <v>74</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>102</v>
+        <v>291</v>
       </c>
       <c r="L85" s="2"/>
-      <c r="M85" t="s" s="2">
-        <v>118</v>
-      </c>
+      <c r="M85" s="2"/>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -9939,13 +9984,13 @@
         <v>74</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>119</v>
+        <v>290</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>74</v>
@@ -9959,10 +10004,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -9985,12 +10030,10 @@
         <v>74</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>95</v>
+        <v>293</v>
       </c>
       <c r="L86" s="2"/>
-      <c r="M86" t="s" s="2">
-        <v>122</v>
-      </c>
+      <c r="M86" s="2"/>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -10040,7 +10083,7 @@
         <v>74</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>125</v>
+        <v>292</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -10060,10 +10103,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10074,7 +10117,7 @@
         <v>80</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>74</v>
@@ -10086,7 +10129,7 @@
         <v>74</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>85</v>
+        <v>295</v>
       </c>
       <c r="L87" s="2"/>
       <c r="M87" s="2"/>
@@ -10097,7 +10140,7 @@
       </c>
       <c r="Q87" s="2"/>
       <c r="R87" t="s" s="2">
-        <v>298</v>
+        <v>74</v>
       </c>
       <c r="S87" t="s" s="2">
         <v>74</v>
@@ -10115,11 +10158,13 @@
         <v>74</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y87" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z87" t="s" s="2">
-        <v>299</v>
+        <v>74</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>74</v>
@@ -10137,13 +10182,13 @@
         <v>74</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>74</v>
@@ -10157,10 +10202,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10168,10 +10213,10 @@
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>74</v>
@@ -10183,10 +10228,12 @@
         <v>74</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="L88" s="2"/>
-      <c r="M88" s="2"/>
+      <c r="M88" t="s" s="2">
+        <v>298</v>
+      </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -10236,13 +10283,13 @@
         <v>74</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="AG88" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>74</v>
@@ -10256,21 +10303,23 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E89" s="2"/>
+      <c r="E89" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F89" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>74</v>
@@ -10282,10 +10331,12 @@
         <v>74</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>303</v>
+        <v>85</v>
       </c>
       <c r="L89" s="2"/>
-      <c r="M89" s="2"/>
+      <c r="M89" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -10311,13 +10362,11 @@
         <v>74</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y89" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y89" s="2"/>
       <c r="Z89" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>74</v>
@@ -10335,26 +10384,1137 @@
         <v>74</v>
       </c>
       <c r="AF89" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AG89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK89" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="90" hidden="true">
+      <c r="A90" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="B90" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="C90" s="2"/>
+      <c r="D90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E90" s="2"/>
+      <c r="F90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K90" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="L90" s="2"/>
+      <c r="M90" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="N90" s="2"/>
+      <c r="O90" s="2"/>
+      <c r="P90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q90" s="2"/>
+      <c r="R90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF90" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AG90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH90" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ90" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK90" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="91" hidden="true">
+      <c r="A91" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="B91" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="C91" s="2"/>
+      <c r="D91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E91" s="2"/>
+      <c r="F91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G91" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K91" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L91" s="2"/>
+      <c r="M91" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="N91" s="2"/>
+      <c r="O91" s="2"/>
+      <c r="P91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q91" s="2"/>
+      <c r="R91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF91" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AG91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH91" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI91" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ91" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK91" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="92" hidden="true">
+      <c r="A92" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="AG89" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH89" t="s" s="2">
+      <c r="B92" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="C92" s="2"/>
+      <c r="D92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="F92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G92" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K92" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L92" s="2"/>
+      <c r="M92" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="N92" s="2"/>
+      <c r="O92" s="2"/>
+      <c r="P92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q92" s="2"/>
+      <c r="R92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X92" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="Y92" s="2"/>
+      <c r="Z92" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF92" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AG92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH92" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ92" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK92" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="93" hidden="true">
+      <c r="A93" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="B93" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="C93" s="2"/>
+      <c r="D93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E93" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="F93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G93" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K93" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L93" s="2"/>
+      <c r="M93" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="N93" s="2"/>
+      <c r="O93" s="2"/>
+      <c r="P93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q93" s="2"/>
+      <c r="R93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF93" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AG93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH93" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ93" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK93" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="94" hidden="true">
+      <c r="A94" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="B94" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="C94" s="2"/>
+      <c r="D94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E94" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="F94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G94" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K94" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L94" s="2"/>
+      <c r="M94" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="N94" s="2"/>
+      <c r="O94" s="2"/>
+      <c r="P94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q94" s="2"/>
+      <c r="R94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF94" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AG94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH94" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ94" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK94" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="95" hidden="true">
+      <c r="A95" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="B95" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="C95" s="2"/>
+      <c r="D95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E95" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="F95" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G95" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K95" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="L95" s="2"/>
+      <c r="M95" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="N95" s="2"/>
+      <c r="O95" s="2"/>
+      <c r="P95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q95" s="2"/>
+      <c r="R95" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="S95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF95" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AG95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH95" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ95" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK95" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="96" hidden="true">
+      <c r="A96" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="B96" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="C96" s="2"/>
+      <c r="D96" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E96" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="F96" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G96" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H96" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I96" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J96" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K96" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L96" s="2"/>
+      <c r="M96" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="N96" s="2"/>
+      <c r="O96" s="2"/>
+      <c r="P96" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q96" s="2"/>
+      <c r="R96" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S96" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T96" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U96" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V96" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W96" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X96" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y96" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z96" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA96" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB96" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC96" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD96" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE96" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF96" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AG96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH96" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI96" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ96" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK96" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="97" hidden="true">
+      <c r="A97" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="C97" s="2"/>
+      <c r="D97" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E97" s="2"/>
+      <c r="F97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G97" t="s" s="2">
         <v>81</v>
       </c>
-      <c r="AI89" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ89" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK89" t="s" s="2">
+      <c r="H97" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I97" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J97" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K97" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L97" s="2"/>
+      <c r="M97" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="N97" s="2"/>
+      <c r="O97" s="2"/>
+      <c r="P97" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q97" s="2"/>
+      <c r="R97" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S97" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T97" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U97" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V97" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W97" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X97" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y97" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z97" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA97" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB97" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC97" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD97" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE97" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF97" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="AG97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH97" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI97" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ97" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK97" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="98" hidden="true">
+      <c r="A98" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="C98" s="2"/>
+      <c r="D98" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E98" s="2"/>
+      <c r="F98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G98" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H98" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I98" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J98" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K98" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="L98" s="2"/>
+      <c r="M98" s="2"/>
+      <c r="N98" s="2"/>
+      <c r="O98" s="2"/>
+      <c r="P98" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q98" s="2"/>
+      <c r="R98" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="S98" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T98" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U98" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V98" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W98" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X98" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="Y98" s="2"/>
+      <c r="Z98" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AA98" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF98" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AG98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH98" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI98" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ98" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK98" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="99" hidden="true">
+      <c r="A99" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="C99" s="2"/>
+      <c r="D99" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E99" s="2"/>
+      <c r="F99" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G99" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H99" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I99" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J99" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K99" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="L99" s="2"/>
+      <c r="M99" s="2"/>
+      <c r="N99" s="2"/>
+      <c r="O99" s="2"/>
+      <c r="P99" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q99" s="2"/>
+      <c r="R99" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S99" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T99" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U99" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V99" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W99" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X99" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y99" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z99" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA99" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB99" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC99" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD99" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE99" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF99" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="AG99" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH99" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI99" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ99" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK99" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="100" hidden="true">
+      <c r="A100" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="C100" s="2"/>
+      <c r="D100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E100" s="2"/>
+      <c r="F100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K100" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="L100" s="2"/>
+      <c r="M100" s="2"/>
+      <c r="N100" s="2"/>
+      <c r="O100" s="2"/>
+      <c r="P100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q100" s="2"/>
+      <c r="R100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF100" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AG100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH100" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ100" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK100" t="s" s="2">
         <v>74</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AK89">
+  <autoFilter ref="A1:AK100">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -10364,7 +11524,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI88">
+  <conditionalFormatting sqref="A2:AI99">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/fusionEntreesCDA/ig/StructureDefinition-fr-cda-dicom-quantite.xlsx
+++ b/fusionEntreesCDA/ig/StructureDefinition-fr-cda-dicom-quantite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T07:29:37+00:00</t>
+    <t>2026-04-20T13:53:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -4842,7 +4842,7 @@
         <v>182</v>
       </c>
       <c r="F35" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>75</v>
